--- a/assets/r04/sheets/敵人角色卡合集.xlsx
+++ b/assets/r04/sheets/敵人角色卡合集.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="敵人角色卡合集" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="凍結獵犬" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="灰燼行者" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="時間迴響" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="守護者殘骸" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,17 +29,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <color rgb="002B5797"/>
-      <sz val="14"/>
+      <sz val="16"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,11 +61,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002B5797"/>
+        <fgColor rgb="00D9E2F3"/>
+        <bgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -58,32 +81,110 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00BBBBBB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BBBBBB"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BBBBBB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BBBBBB"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,249 +550,1843 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>敵人角色卡合集</t>
-        </is>
-      </c>
-    </row>
+          <t>【凍結獵犬】威脅等級 3 — 變異生物(中型)</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="n"/>
+      <c r="C1" s="10" t="n"/>
+      <c r="D1" s="10" t="n"/>
+      <c r="E1" s="10" t="n"/>
+      <c r="F1" s="11" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>類型</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>威脅等級</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>屬性/能力</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>弱點</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
-      </c>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>基本資訊</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>咒靈</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>咒靈</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>不定</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>純粹負面情感實體化</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>反轉術式/正面情緒</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>由人類負面情感誕生的純粹情感集合體</t>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>凍結獵犬</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>變異生物(中型)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>詛咒師</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>詛咒師</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>不定</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>術式/咒具運用</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>依個體而異</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>非法使用咒力的集團或精神發病者</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>變異生物</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>變異生物</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>低~高</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>肉體/生態異常</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>依物種而異</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>來自郊區或荒野深處的危險生物</t>
-        </is>
-      </c>
-    </row>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>威脅等級: 3</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>各凍結區(常見)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>刁民</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>刁民</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>低~中</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>洗腦/脅迫/暴力</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>談判/制服</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>窮山惡水出壞人，非咒術師但仍危險</t>
-        </is>
-      </c>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="11" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>環境災害</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>環境</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>不定</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>範圍性傷害</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>防護/撤離</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>污染、天災或人禍造成的危機</t>
-        </is>
-      </c>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>曾是軍用犬，時間凍結扭曲了牠的形體——左半身永遠停留在解凍瞬間，肌肉在皮膚下蠕動如活物。</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>未知威脅</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>情報不足</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>偵查先行</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>由情報/預警部門負責偵查的未明威脅</t>
-        </is>
-      </c>
+      <c r="A9" s="14" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="16" t="n"/>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>屬性</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="11" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>屬性</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>修正值</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>速度（SPD）</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>知覺（PER）</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>膽量（GUT）</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>技術（TEC）</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>衍生屬性</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="11" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>生命值（HP）</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>防禦值（AC）</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>移動力</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>恐慌閾值</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>先攻修正</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>攻擊</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="11" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>攻擊名稱</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>命中公式</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>傷害</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>射程</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>特殊效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>撲咬</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>d20+速度修正值 vs 防禦值（AC）</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>2d6 物理</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>近戰</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>目標速度難度（DC）12否則倒地</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>爪擊</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>d20+速度修正值 vs 防禦值（AC）</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>1d6+3 物理</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>近戰</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>時間嚎叫</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>特殊</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>5x5格</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>範圍內膽量難度（DC）14否則慌亂</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>特殊能力</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="11" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>解凍追跡：感知10格內最近解凍位置</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="11" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>凍結抗性：被重新凍結時持續時間減半</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="11" t="n"/>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>戰利品</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="11" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>時間結晶碎片(1d3), 軍用項圈(膽量對抗動物+1)</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="11" t="n"/>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>戰術行為</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="11" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>解凍時優先攻擊最近的非凍結目標</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="11" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>生命值（HP）&lt;50%後退至安全距離使用時間嚎叫</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="11" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A8:F9"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A25:F25"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>【灰燼行者】威脅等級 4 — 變異生物(大型)</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="n"/>
+      <c r="C1" s="10" t="n"/>
+      <c r="D1" s="10" t="n"/>
+      <c r="E1" s="10" t="n"/>
+      <c r="F1" s="11" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>基本資訊</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="11" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>灰燼行者</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>變異生物(大型)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>威脅等級: 4</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>燃燒後的凍結區</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="11" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>一頭被凍結在燃燒瞬間的巨狼。半身焦黑、半身凍結。牠的每一步都在灰燼中留下燃燒的足跡。</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="13" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="16" t="n"/>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>屬性</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="11" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>屬性</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>修正值</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>速度（SPD）</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>知覺（PER）</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>膽量（GUT）</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>技術（TEC）</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>衍生屬性</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="11" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>生命值（HP）</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>防禦值（AC）</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>移動力</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>恐慌閾值</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>先攻修正</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>攻擊</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="11" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>攻擊名稱</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>命中公式</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>傷害</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>射程</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>特殊效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>灰燼撲擊</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>d20+速度修正值 vs 防禦值（AC）</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>2d8 物理+1d4火焰</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>近戰</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>目標需膽量難度（DC）12否則慌亂</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>灼熱尾擊</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>d20+速度修正值 vs 防禦值（AC）</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>1d8+3 火焰</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>近戰(橫掃3格)</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>點燃易燃物</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>灰燼咆哮</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>特殊</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>前方錐形5格</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>膽量難度（DC）16否則恐慌+火焰傷害1d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>特殊能力</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="11" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>燃燒光環：相鄰格每回合1點火焰傷害</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="11" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>火焰免疫：不受火焰/高溫傷害</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="11" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>畏水：接觸水時速度-3 (1回合)</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="11" t="n"/>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>戰利品</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="11" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>灰燼結晶(特殊時間結晶，價值3普通結晶), 焦化毛皮(護甲材料)</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="11" t="n"/>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>戰術行為</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="11" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>優先攻擊持有火源或發光物品的目標</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="11" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>利用燃燒光環壓縮玩家移動空間</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="11" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>受傷後變得更具攻擊性而非撤退</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="11" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A8:F9"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A25:F25"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>【時間迴響】威脅等級 3 — 環境威脅</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="n"/>
+      <c r="C1" s="10" t="n"/>
+      <c r="D1" s="10" t="n"/>
+      <c r="E1" s="10" t="n"/>
+      <c r="F1" s="11" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>基本資訊</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="11" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>時間迴響</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>環境威脅</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>威脅等級: 3</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>高密度時間結晶區域</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="11" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>凍結區內的「時間記憶」——過去的解凍事件留下的能量殘影。它沒有實體，但能重播過去解凍瞬間的致命片段。</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="13" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="16" t="n"/>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>攻擊</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="11" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>攻擊名稱</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>命中公式</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>傷害</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>射程</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>特殊效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>迴響衝擊</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>1d8 時間傷害</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>觸及範圍(5格)</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>無視護甲</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>記憶重播</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>特殊</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>區域</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>重播該區域上一次解凍中的最危險事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>特殊能力</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="11" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>不可攻擊：時間迴響無法被物理攻擊傷害</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="11" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>時間結晶可驅散：消耗1結晶使其消失1d4回合</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="11" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>感知預兆：知覺難度（DC）15可預測其下一次移動方向</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="11" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>戰利品</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="11" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>消散後留下1d3時間結晶</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="11" t="n"/>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>戰術行為</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="11" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>在時間結晶密集處自動生成</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="11" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>每1d4回合向最近的生物移動3格</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="11" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>接近時玩家感到時間感知扭曲</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="11" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A8:F9"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A25:F25"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>【守護者殘骸】威脅等級 5 — 機械威脅</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="n"/>
+      <c r="C1" s="10" t="n"/>
+      <c r="D1" s="10" t="n"/>
+      <c r="E1" s="10" t="n"/>
+      <c r="F1" s="11" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>基本資訊</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="11" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>守護者殘骸</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>機械威脅</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>威脅等級: 5</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>軍事設施凍結區</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="11" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>一台凍結中的軍用防禦機器人。凍結讓它的瞄準系統卡在最後一刻——但解凍時它的火力依然致命。雙臂配備旋轉機槍。</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="13" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="16" t="n"/>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>屬性</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="11" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>屬性</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>修正值</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>速度（SPD）</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>知覺（PER）</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>膽量（GUT）</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>技術（TEC）</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>衍生屬性</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="11" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>生命值（HP）</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>防禦值（AC）</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>移動力</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>恐慌閾值</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>先攻修正</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>攻擊</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="11" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>攻擊名稱</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>命中公式</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>傷害</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>射程</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>特殊效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>旋轉機槍</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>d20+技術修正值 vs 防禦值（AC）</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>3d6 物理</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>15格</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>壓制射擊：目標下回合移動力-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>榴彈發射器</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>d20+技術修正值 vs 防禦值（AC）</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>4d6 物理</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>10格(3x3範圍)</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>每場戰鬥限1發</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>電磁脈衝</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>特殊</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>5x5格</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>範圍內電子設備失效2回合，探測器失靈</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>特殊能力</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="11" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>裝甲：物理傷害-3</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="11" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>凍結核心：被時間結晶裝置擊中時，癱瘓1d4回合(技術難度（DC）14)</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="11" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>自毀程序：生命值（HP）&lt;25%時啟動，3回合後爆炸(6d6/5x5格)</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="11" t="n"/>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>戰利品</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="11" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>軍用級零件(價值5結晶), 機槍(若拆除成功), 加密數據晶片(世界觀線索)</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="11" t="n"/>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>戰術行為</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="11" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>優先消滅移動目標</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="11" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>保持距離(後退至最大射程)</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="11" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>自毀啟動後停止攻擊，全力保護核心</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="11" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A8:F9"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A25:F25"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>